--- a/report/mearsuring-profile/MP-06_Performance_Burst_Efficiency.xlsx
+++ b/report/mearsuring-profile/MP-06_Performance_Burst_Efficiency.xlsx
@@ -585,9 +585,8 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>▶  MP-06 Performance Burst - Efficiency &amp; Power Map (Bản Đồ Công Suất &amp; Hiệu Suất Tăng Tốc)  |  Tests: PERF-003, PERF-004, PERF-007, PERF-008, LOAD-004, LOAD-008
-Description (EN): Ultra-high-speed (10ms) voltage, current, and torque data collection across all travel drives and battery output during peak acceleration bursts to compile a power map.
-Mô tả (VI): Ghi dữ liệu tốc độ cực nhanh (10ms) dòng điện, điện áp, mô-men xoắn của cả 4 động cơ di chuyển (M1-M4), tốc độ động cơ (Velocity) và BMS để xây dựng bản đồ công suất xe.</t>
+          <t>▶  MP-06 Performance Burst - Efficiency &amp; Power Map  |  Tests: PERF-003, PERF-004, PERF-007, PERF-008, LOAD-004, LOAD-008
+Description: Ultra-high-speed (10ms) voltage, current, and torque data collection across all travel drives and battery output during peak acceleration bursts to compile a power map.</t>
         </is>
       </c>
     </row>

--- a/report/mearsuring-profile/MP-06_Performance_Burst_Efficiency.xlsx
+++ b/report/mearsuring-profile/MP-06_Performance_Burst_Efficiency.xlsx
@@ -581,8 +581,15 @@
   </sheetPr>
   <dimension ref="A1:J24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18.28515625" customWidth="1" min="1" max="1"/>
+    <col width="42.7109375" customWidth="1" min="2" max="2"/>
+    <col width="29.28515625" customWidth="1" min="4" max="4"/>
+    <col width="13.42578125" customWidth="1" min="7" max="7"/>
+    <col width="32" customWidth="1" min="9" max="9"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="34.5" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>▶  MP-06 Performance Burst - Efficiency &amp; Power Map  |  Tests: PERF-003, PERF-004, PERF-007, PERF-008, LOAD-004, LOAD-008
@@ -642,7 +649,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="36" customHeight="1">
+    <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>batt_voltage_travelA</t>
@@ -686,7 +693,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="48" customHeight="1">
+    <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
           <t>current_travelA</t>
@@ -730,7 +737,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="36" customHeight="1">
+    <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t>batt_voltage_travelB</t>
@@ -774,7 +781,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="48" customHeight="1">
+    <row r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
           <t>current_travelB</t>
@@ -818,7 +825,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="36" customHeight="1">
+    <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
           <t>batt_voltage_travelC</t>
@@ -862,7 +869,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="48" customHeight="1">
+    <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
           <t>current_travelC</t>
@@ -906,7 +913,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="36" customHeight="1">
+    <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
           <t>batt_voltage_travelD</t>
@@ -950,7 +957,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="48" customHeight="1">
+    <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
           <t>current_travelD</t>
@@ -994,7 +1001,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="60" customHeight="1">
+    <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
           <t>torque_travelA</t>
@@ -1038,7 +1045,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="36" customHeight="1">
+    <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
           <t>torque_travelB</t>
@@ -1082,7 +1089,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="36" customHeight="1">
+    <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
           <t>torque_travelC</t>
@@ -1126,7 +1133,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="36" customHeight="1">
+    <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
           <t>torque_travelD</t>
@@ -1170,7 +1177,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="36" customHeight="1">
+    <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
           <t>travel_rpm_M1</t>
@@ -1214,7 +1221,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="36" customHeight="1">
+    <row r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
           <t>travel_rpm_M2</t>
@@ -1258,7 +1265,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="36" customHeight="1">
+    <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
           <t>travel_rpm_M3</t>
@@ -1302,7 +1309,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="36" customHeight="1">
+    <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
           <t>travel_rpm_M4</t>
@@ -1346,7 +1353,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="48" customHeight="1">
+    <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
           <t>bms_voltage</t>
@@ -1390,7 +1397,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="60" customHeight="1">
+    <row r="20">
       <c r="A20" s="8" t="inlineStr">
         <is>
           <t>bms_current</t>
@@ -1434,7 +1441,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="60" customHeight="1">
+    <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
           <t>vehicle_speed_gps</t>
@@ -1478,7 +1485,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="48" customHeight="1">
+    <row r="22">
       <c r="A22" s="8" t="inlineStr">
         <is>
           <t>vehicle_speed_encoder</t>
@@ -1522,7 +1529,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="60" customHeight="1">
+    <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
           <t>operating_mode</t>
@@ -1566,7 +1573,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="60" customHeight="1">
+    <row r="24">
       <c r="A24" s="8" t="inlineStr">
         <is>
           <t>hoist_load_kg</t>
